--- a/docs/downloads/05/tbl_water_alaotra_mangabe.xlsx
+++ b/docs/downloads/05/tbl_water_alaotra_mangabe.xlsx
@@ -405,12 +405,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,12 +537,6 @@
         <is>
           <t>Alaotra - Tous</t>
         </is>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>
